--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_24-04-2026.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_24-04-2026.xlsx
@@ -513,17 +513,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£13.00</t>
+          <t>£14.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£13.00</t>
+          <t>£14.50</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£13.00</t>
+          <t>£14.50</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -585,17 +585,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£14.06</t>
+          <t>£17.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£14.06</t>
+          <t>£17.00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£14.06</t>
+          <t>£17.00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -657,17 +657,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£18.33</t>
+          <t>£21.15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£18.33</t>
+          <t>£21.15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£18.33</t>
+          <t>£21.15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -729,17 +729,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£18.44</t>
+          <t>£21.90</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£18.44</t>
+          <t>£21.90</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£18.44</t>
+          <t>£21.90</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -801,17 +801,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£23.65</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£23.65</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£23.65</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -873,17 +873,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£26.51</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£26.51</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£26.51</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -945,17 +945,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£26.50</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£26.50</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£26.50</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1017,17 +1017,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£29.74</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£29.74</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£29.74</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1089,17 +1089,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£32.52</t>
+          <t>£37.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£32.52</t>
+          <t>£37.75</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£32.52</t>
+          <t>£37.75</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£32.50</t>
+          <t>£36.95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£32.50</t>
+          <t>£36.95</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£32.50</t>
+          <t>£36.95</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1305,17 +1305,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£47.32</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£47.32</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£47.32</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1449,17 +1449,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£47.85</t>
+          <t>£57.20</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£47.85</t>
+          <t>£57.20</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£47.85</t>
+          <t>£57.20</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£49.00</t>
+          <t>£57.23</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£49.00</t>
+          <t>£57.23</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£49.00</t>
+          <t>£57.23</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1593,17 +1593,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£48.52</t>
+          <t>£56.28</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>£48.52</t>
+          <t>£56.28</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>£48.52</t>
+          <t>£56.28</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
